--- a/demo/fact_sample.xlsx
+++ b/demo/fact_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,12 +541,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C 74.00.a</t>
+          <t>C_76.00.a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0030</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55000</v>
+        <v>6800000</v>
       </c>
     </row>
     <row r="8">
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0020</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6800000</v>
+        <v>5400000</v>
       </c>
     </row>
     <row r="9">
@@ -586,7 +586,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>0030</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -595,27 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5400000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>C_76.00.a</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0030</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0010</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1.32</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
